--- a/Result/profitability/6212.xlsx
+++ b/Result/profitability/6212.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>-0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03375</v>
+        <v>1.1175</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -766,7 +766,7 @@
         <v>0.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09125</v>
+        <v>0.6550000000000001</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -873,7 +873,7 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5862500000000002</v>
+        <v>0.3737500000000001</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -980,7 +980,7 @@
         <v>-0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2975000000000001</v>
+        <v>0.2887500000000001</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1087,7 +1087,7 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2287500000000001</v>
+        <v>0.2575000000000001</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1204,7 +1204,7 @@
         <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3550000000000001</v>
+        <v>0.3387500000000001</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1321,7 +1321,7 @@
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2750000000000001</v>
+        <v>0.2962500000000001</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9586,6 +9586,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6212</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>336</v>
+      </c>
+      <c r="D75" t="n">
+        <v>203</v>
+      </c>
+      <c r="E75" t="n">
+        <v>133</v>
+      </c>
+      <c r="F75" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="G75" t="n">
+        <v>102</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>30.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>95</v>
+      </c>
+      <c r="K75" t="n">
+        <v>58</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.48125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4249999999999998</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05323396326856544</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.07000000000000006</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1093750000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.8100000000000023</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02089783281733748</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
